--- a/output_excel/17176207.xlsx
+++ b/output_excel/17176207.xlsx
@@ -32,11 +32,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C6500"/>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="009C6500"/>
     </font>
   </fonts>
   <fills count="5">
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -563,27 +563,19 @@
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>P6 | CONEX. | 112,5KVA | 37,5KVA | 112,5KVA | 112,5KVA | 71 | AVENIDA | 37,5KVA | BT | 37,5KVA | 3x336AN | 112,5KVA | 112,5KVA | 112,5KVA | (DCIM) | 3x336AN | 112,5KVA | CAMPO | 112,5KVA | QX16 | RAMAL | 112,5KVA | 112,5KVA | CABOS | (DCIM) | 30K | 112,5KVA | 30K | 30K | (DCIM) | 37,5KVA | AV. | 400816F | 30K | CONEX. | 112,5KVA | BF-A | 30K | 1AF(1) | BF-A | C09x600,L1(2),IP112,5KVACE4 | 3x336AN | (DCIM) | AVENIDA | 112,5KVA112,5KVA | (DCIM) | (DCIM) | 112,5KVA | IP | 30K | SMTG112,5KVAL1(2) | 37,5KVA | (KL) | 30K | 112,5KVA | 3x336AN | AV. | ANCORAR | X6 | 30K | ANCORAR | Z | 112,5KVA | 30K | 112,5KVA | BF-A | (DCIM) | 112,5KVA | CONEX. | (DCIM) | (DCIM) | 112,5KVA | (DCIM) | 112,5KVA | 175ET005296879 | 14M | BF-A | (DCIM) | (DCIM) | (DCIM) | 30K | LC | 112,5KVA | 1x3x120(70)AX | CONEX. | CONEX. | BT | 37,5KVA | (DCIM) | 112,5KVA | 112,5KVA | 30K | 30K | 112,5KVA | 37,5KVA | 112,5KVA | CONEX. | CONEX. | 30K | 30K | CONEX. | BT | 112,5KVA | P5 | (DCIM)</t>
+          <t>(DCIM) | (DCIM) | ANCORAR | (DCIM) | (DCIM) | BF-A | ANCORAR | BF-A | 0 | 1AF(1) | (KL) | (DCIM) | 2 | 8 | CABOS | 2 | 0 | 6 | 2 | 6 | 1 | CONEX. | 600112,5KVACE4 | 12 | 6 | (DCIM) | 7 | 112,5KVA | 7 | 1 | CAMPO | 7 | 71 | 112,5KVA | 1 | QX16 | 1 | BT | 1 | BF-A | 14M | AVENIDA</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>REVISAR</t>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -620,13 +612,13 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | V1-2 | BT | 3x185AX(5AZN) | MT | 112,5KVA | CONEX. | 30K | 112,5KVA | 30K | 112,5KVA | 30K | (DCIM) | 112,5KVA112,5KVA | (DCIM) | (KL) | 112,5KVA | 1AF(1) | AVENIDA | (KL) | 112,5KVA | (DCIM) | (DCIM) | CABOS | 112,5KVA | 30K112,5KVAIP | (DCIM) | SMAN | 14.72M | CONEX. | 112,5KVA | 3x336AN | Q/R | BF-A | 112,5KVA | 14.72M | 112,5KVA | 112,5KVA | C12X1000112,5KVACE4112,5KVACE3112,5KVAIP | (DCIM) | 112,5KVA | CONEX. | 30K | BT | BF-A | 112,5KVA | 112,5KVA | 3x336AN | (DCIM) | DG</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="n">
+          <t>1x3x120(70)AX | BT | 3x185AX(5AZN) | MT | CONEX. | 1 | 2 | 0 | 1 | 0 | 0 | (DCIM) | 112,5KVA2 | SMAN | (DCIM) | AVENIDA | (KL) | 1AF(1) | 112,5KVA | (KL) | (DCIM) | 1 | 14.72M | CABOS | 3112,5KVAIP | (DCIM) | 2 | C12X1000112,5KVACE4112,5KVACE3112,5KVAIP | (DCIM) | 14.72M | CONEX. | 1 | Q/R | 6 | 1 | BF-A | 1</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -661,13 +653,13 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>P1-11 | CONEX. | (DCIM) | (DCIM) | (DCIM) | (DCIM) | MT | ANCORAR | ANCORAR | B1F | BF-A | BF-A | BT | 3x185AX(5AZN) | 37,5KVA | 400816F | 1x3x120(70)AX | Nº307/SNº | 112,5KVA | 30K | 30K | 112,5KVA | P2 | 112,5KVA | BF-A | 112,5KVA | 112,5KVA | 30K | 3x336AN | 3x336AN | CAMPO | 37,5KVA | (DCIM) | (DCIM) | 37,5KVA | 112,5KVA | (DCIM) | 112,5KVA | 112,5KVA | (DCIM) | NF | BT | 37,5KVA | ANCORAR | ANCORAR | 112,5KVA | AVENIDA | 175ET005296879 | BF-A | BF-A | 3x336AN | 30K | 30K | 1x2x4AC | 30K | 30K | (DCIM) | 112,5KVA | 112,5KVA | BF-A | 112,5KVA | 3x336AN | P31 | CAMPO | 3x336AN | 30.43M | 112,5KVA | 30.43M | 37,5KVA | 37,5KVA | 112,5KVA | DG | 112,5KVA | 71 | AVENIDA | 175ET005296879</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n">
+          <t>0 | 0 | 1 | 0 | CONEX. | (KL) | 112,5KVA2 | 112,5KVA | 1 | 2 | (KL) | (DCIM) | 2 | 1AF(1) | 1 | (DCIM) | (DCIM) | (DCIM) | (DCIM) | AVENIDA | CABOS | 6 | 1 | BF-A | CONEX. | 3112,5KVAIP | 1 | Q/R | 2 | (DCIM) | 1 | 0 | 1 | BF-A | CONEX. | 1 | BT | 6 | (DCIM) | 1 | 1x3x120(70)AX | BT | 3x185AX(5AZN) | MT | 14.72M</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -710,13 +702,13 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>P5 | SMTG112,5KVAL1(2) | (DCIM) | (DCIM) | 112,5KVA | 112,5KVA | 112,5KVA | 30K | AV. | 112,5KVA | X6 | 30K | (DCIM) | 112,5KVA | 30K | BT | 30K | 30K | AV. | CONEX. | (DCIM) | 30K | 30K | 112,5KVA | 3x336AN | 30K | 112,5KVA | 30K | CONEX. | 37,5KVA | Z | 30K | 30K | (DCIM) | 112,5KVA | BT | CONEX. | CONEX. | (DCIM) | (DCIM) | 112,5KVA | BF-A | 112,5KVA | 112,5KVA | AVENIDA | Z | 1x3x120(70)AX | 112,5KVA | 175ET005296879 | 3x336AN | CONEX. | (DCIM) | 112,5KVA112,5KVA | 30K | (DCIM) | 112,5KVA | 30K | CONEX. | CONEX. | 112,5KVA | 112,5KVA | 112,5KVA | BT | 30K | 30K | P6 | B1F | (DCIM) | 37,5KVA | 37,5KVA | CONEX. | (DCIM) | 30K | 1x3x120(70)AX | (DCIM) | IP | AV. | 112,5KVA | 3x336AN | 37,5KVA | 112,5KVA | 30K | CONEX. | AVENIDA | 30K | 112,5KVA | 30K | 112,5KVA | 30K | (DCIM) | 45KVA | (DCIM) | 112,5KVA | 30K | 3x336AN | BT | 3x336AN | BF-A | 112,5KVA | 112,5KVA | 112,5KVA | 112,5KVA | 37,5KVA | AV. | 71 | 37,5KVA | 112,5KVA | (DCIM) | C10x600,B1M,M3F | C12x300,CE-SH,ET4A,IP112,5KVAET4A112,5KVAIP | CONEX. | 112,5KVA | CONEX. | 37,5KVA | 112,5KVA</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n">
+          <t>SMTG112,5KVAL1(2) | (DCIM) | (DCIM) | 1 | 5 | 2 | 3 | AV. | 1 | X6 | 3 | (DCIM) | 5 | 3 | BT | 3 | 0 | AV. | CONEX. | (DCIM) | 3 | 0 | 1 | 3x336AN | 3 | 112,5KVA | 0 | CONEX. | 7 | Z | 3 | 0 | (DCIM) | 112,5KVA | BT | CONEX. | CONEX. | (DCIM) | (DCIM) | 5 | BF-A | 112,5KVA | 112,5KVA | AVENIDA | Z | 1x3x120(70)AX | 5 | 17 | 3x336AN | CONEX. | (DCIM) | 2112,5KVA | 0 | (DCIM) | 1 | 3 | CONEX. | CONEX. | 1 | 1 | 2 | BT | 3 | 0 | B1F | (DCIM) | 7 | 7 | CONEX. | (DCIM) | 0 | 1x3x120(70)AX | (DCIM) | IP | AV. | 112,5KVA | 6 | 7 | 112,5KVA | 0 | CONEX. | AVENIDA | 3 | 1 | 0 | 2 | 3 | (DCIM) | 45KVA | (DCIM) | 1 | 0 | 6 | BT | 6 | BF-A | 5 | 2 | 112,5KVA | 1 | 7 | AV. | 71 | 7 | 1 | (DCIM) | C10x600,B1M,M3F | C12x300,CE-SH,ET4A,IP112,5KVAET4A112,5KVAIP | CONEX. | 112,5KVA | CONEX. | 7 | 1</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
@@ -751,13 +743,13 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>(DCIM) | (DCIM) | P2 | P1-11 | (DCIM) | (DCIM) | CONEX. | ANCORAR | ANCORAR | BF-A | BF-A | (DCIM) | (DCIM) | 3x336AN | 30K | 1x2x4AC | (DCIM) | (DCIM) | 30K | 30K | 30K | MT | ANCORAR | 112,5KVA | 112,5KVA | ANCORAR | 112,5KVA | BF-A | 3x336AN | 3x336AN | BF-A | CAMPO | 3x185AX(5AZN) | B1F | 37,5KVA | 37,5KVA | 400816F | BT | 37,5KVA | 112,5KVA | 112,5KVA | 30K | 71 | 1x3x120(70)AX | 30K | Nº307/SNº | 37,5KVA | 112,5KVA | NF | 175ET005296879 | 112,5KVA | 112,5KVA | 112,5KVA | 112,5KVA | 3x336AN | BF-A | 112,5KVA | 112,5KVA | 3x336AN | BF-A | 30K | 37,5KVA | 37,5KVA | CAMPO | 112,5KVA | P31 | 112,5KVA | 112,5KVA | 37,5KVA | BT | 175ET005296879 | 112,5KVA | AVENIDA</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+          <t>(DCIM) | (DCIM) | (DCIM) | (DCIM) | ANCORAR | CONEX. | ANCORAR | BF-A | BF-A | 4 | (DCIM) | 3 | 6 | (DCIM) | 3 | MT | 3 | (DCIM) | 0 | (DCIM) | 1 | 1 | ANCORAR | 3x185AX(5AZN) | 112,5KVA | 6 | ANCORAR | 6 | B1F | BF-A | 7 | CAMPO | 7 | BT | BF-A | NF | 1 | BF-A | 1x3x120(70)AX | 112,5KVA | 8 | 71 | 7 | 7 | 3 | 112,5KVA | 3 | 07 | 1 | 175ET005296879 | 2 | 1 | 1 | BF-A | 1 | 3 | 6 | 112,5KVA | 6 | 7 | 7 | CAMPO | 1 | 1 | 112,5KVA | 7 | BT | 17 | 1 | 5 | AVENIDA</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -788,27 +780,19 @@
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>P4-30 | CMB | 175ET005296879 | 112,5KVA | 3x336AN | II | 1x2x4AC | 3x336AN | CABOS | (DCIM) | 3x336AN | BT | ANCORAR | (DCIM) | YOSHIDA | 112,5KVA | 112,5KVA | 112,5KVA | (KL) | 112,5KVA | CONEX. | ESTR. | 3x336AN | (DCIM) | (DCIM) | 1x2x4AC | 1x2x4AC | AV. | 30K | 112,5KVA | 112,5KVA | 175ET005296879 | 1x2x4AC | (DCIM) | (DCIM) | 30K | (DCIM) | BT | 3x336AN | 564661112,5KVAD_TF | 112,5KVA | Z | 30K | (DCIM) | CONEX. | 112,5KVA | MV | 37,5KVA | 112,5KVA | (DCIM) | AVENIDA | 1x2x4AC | 1x2x4AC | AV. | (DCIM) | 112,5KVA | 30K | 1x2x4AC | B1F | 15KV_1T(ABC) | C12x300,CE-SH,ET4A,IP112,5KVAET4A112,5KVAIP | 112,5KVA | BT | CONEX. | CONEX. | 112,5KVA | 1x3x120(70)AX | CONEX. | 112,5KVA | CONEX. | 30K | 30K | 30K | (DCIM) | 37,5KVA | CONEX. | (DCIM) | 112,5KVA | 37,5KVA | 112,5KVA | 30K | 112,5KVA | 112,5KVA | 112,5KVA | CONEX. | 112,5KVA | 112,5KVA | TX10 | 1x2x4AC | 30K | Z | 112,5KVA | BF-A | 30K | 112,5KVA | 4660 | (DCIM) | CONEX. | 3x336AN | 37,5KVA | 30K | BT | 30K | 112,5KVA | BF-A | CONEX. | (DCIM) | C10x600,B1M,M3F | TX16 | 1x3x120(70)AX | 29M | 112,5KVA | (DCIM) | 30K</t>
+          <t>1 | RAMAL | TRAFO | 2 | TX16 | 2x1/0AN(4ANA) | 1 | TX10 | INSTALAÇÃO | BF-A | REAPROVEITAR | 36M | LC | BF-A | MV | 29M | 15KV_1T(ABC) | 175ET005296879 | 564661112,5KVAD_TF | (DCIM) | 12 | CONEX. | 6 | 0 | 0 | 112,5KVA</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>REVISAR</t>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -849,13 +833,13 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4660 | ESTR. | 3x336AN | YOSHIDA | 112,5KVA | C09x300,SMPI,L1(2),IP | P31 | II | FERRAGEM112,5KVA(KL) | BT | 30K | (DCIM) | CONEX. | BT | 37,5KVA | 30K | 112,5KVA | 175ET005296879 | CONEX. | 30.43M | BF-A | (DCIM) | 112,5KVA | 25KVA | C09x300,SMPI,IP | 112,5KVA | CMB | Z | BT | 112,5KVA | B1F | NF | CONEX. | 30K | CONEX. | 3x336AN | 112,5KVA | 112,5KVA | 30K | (DCIM) | C12X600112,5KVACE4112,5KVABF-A112,5KVAIP | (DCIM) | 30.43M | 37,5KVA | 564660 | 1x2x4AC | P4-30 | 30K | 10M | 1x3x120(70)AX | 112,5KVA | BF-A | 112,5KVA | 30K | BF-A | 1x2x4AC | 112,5KVA | AV. | CONEX. | BF-A | 1x2x4AC | 1x2x4AC | 1x2x4AC | 3x336AN | TX10 | 112,5KVA | (DCIM) | CABOS | AV. | 112,5KVA | 1x2x4AC</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
+          <t>(DCIM) | (DCIM) | (DCIM) | ANCORAR | (DCIM) | BF-A | ANCORAR | BF-A | 4 | 3 | 3 | 1 | 3 | 6 | 1 | 0 | 6 | 6 | CONEX. | 7 | BF-A | 112,5KVA | 7 | 1 | CAMPO | 7 | 71 | 112,5KVA | MT | (DCIM) | 1 | (DCIM) | NF | 1 | 3x185AX(5AZN) | 175ET005296879 | (DCIM) | (DCIM) | B1F | ANCORAR | BT | ANCORAR | 1x3x120(70)AX | BF-A | BF-A | C09x300,SMPI,IP | 8 | 5 | 112,5KVA | 7 | C12X600112,5KVACE4112,5KVABF-A112,5KVAIP | 2 | BF-A | 3 | 3 | 3 | BT | 07 | (DCIM) | 1 | BF-A | 1 | FERRAGEM112,5KVA(KL)</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>

--- a/output_excel/17176207.xlsx
+++ b/output_excel/17176207.xlsx
@@ -470,20 +470,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,35 +512,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Rua / Avenida</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ancoragem</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Lado Forte</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Metragem</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Altura Poste</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Informações</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Confiança</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Corrigido IA</t>
         </is>
@@ -565,20 +583,23 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>(DCIM) | (DCIM) | ANCORAR | (DCIM) | (DCIM) | BF-A | ANCORAR | BF-A | 0 | 1AF(1) | (KL) | (DCIM) | 2 | 8 | CABOS | 2 | 0 | 6 | 2 | 6 | 1 | CONEX. | 600112,5KVACE4 | 12 | 6 | (DCIM) | 7 | 112,5KVA | 7 | 1 | CAMPO | 7 | 71 | 112,5KVA | 1 | QX16 | 1 | BT | 1 | BF-A | 14M | AVENIDA</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>CONEX. 1 7 2 CS's (DCIM) (DCIM) 12 1AF(1) CONEX. (KL) 600112,5KVACE4 | P6 1 2 QX16 RAMAL 2 V1-3 14M LC P5 | BT 112,5KVA CAMPO 6 2 0 8 2 0 2 V1-3 | B1F (DCIM) BT BT 1 3 CONEX. CONEX. 3 7 CONEX. 0 1 112,5KVA 2 CONEX. 0 (DCIM) (DCIM) 5 7 112,5KVA 1x3x120(70)AX CRUZ 112,5KVA 1x4ANA | 112,5KVA 5 2 V1-3 6 | 27.63m P5</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -603,27 +624,30 @@
           <t>V1-2</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>14.72m</t>
-        </is>
-      </c>
+      <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | BT | 3x185AX(5AZN) | MT | CONEX. | 1 | 2 | 0 | 1 | 0 | 0 | (DCIM) | 112,5KVA2 | SMAN | (DCIM) | AVENIDA | (KL) | 1AF(1) | 112,5KVA | (KL) | (DCIM) | 1 | 14.72M | CABOS | 3112,5KVAIP | (DCIM) | 2 | C12X1000112,5KVACE4112,5KVACE3112,5KVAIP | (DCIM) | 14.72M | CONEX. | 1 | Q/R | 6 | 1 | BF-A | 1</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
+          <t>14.72m</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>3x185AX(5AZN) 14.72M 14.72M | 1 1 BT JUQ CONEX. CONEX. 1 1 0 6 2 V1-3 2 V1-3 1 1 6 2 (DCIM) (DCIM) | MT | BT V1-2 1x3x120(70)AX | CONEX. MT 3x185AX(5AZN) | P2 | DG 1 1 7 1 7 6 7 6 | 175ET005296879 112,5KVA CAMPO 112,5KVA 6 1 3 3 3 4 2 V1-3</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -651,20 +675,31 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0 | 0 | 1 | 0 | CONEX. | (KL) | 112,5KVA2 | 112,5KVA | 1 | 2 | (KL) | (DCIM) | 2 | 1AF(1) | 1 | (DCIM) | (DCIM) | (DCIM) | (DCIM) | AVENIDA | CABOS | 6 | 1 | BF-A | CONEX. | 3112,5KVAIP | 1 | Q/R | 2 | (DCIM) | 1 | 0 | 1 | BF-A | CONEX. | 1 | BT | 6 | (DCIM) | 1 | 1x3x120(70)AX | BT | 3x185AX(5AZN) | MT | 14.72M</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>SMAN C12X1000112,5KVACE4112,5KVACE3112,5KVAIP | BT V1-2 1x3x120(70)AX | DG 1 1 7 1 7 6 7 6 | 2 CS's CACHIMBO APARECIDINHA | 112,5KVA (DCIM)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -690,30 +725,33 @@
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>SMTG112,5KVAL1(2) | (DCIM) | (DCIM) | 1 | 5 | 2 | 3 | AV. | 1 | X6 | 3 | (DCIM) | 5 | 3 | BT | 3 | 0 | AV. | CONEX. | (DCIM) | 3 | 0 | 1 | 3x336AN | 3 | 112,5KVA | 0 | CONEX. | 7 | Z | 3 | 0 | (DCIM) | 112,5KVA | BT | CONEX. | CONEX. | (DCIM) | (DCIM) | 5 | BF-A | 112,5KVA | 112,5KVA | AVENIDA | Z | 1x3x120(70)AX | 5 | 17 | 3x336AN | CONEX. | (DCIM) | 2112,5KVA | 0 | (DCIM) | 1 | 3 | CONEX. | CONEX. | 1 | 1 | 2 | BT | 3 | 0 | B1F | (DCIM) | 7 | 7 | CONEX. | (DCIM) | 0 | 1x3x120(70)AX | (DCIM) | IP | AV. | 112,5KVA | 6 | 7 | 112,5KVA | 0 | CONEX. | AVENIDA | 3 | 1 | 0 | 2 | 3 | (DCIM) | 45KVA | (DCIM) | 1 | 0 | 6 | BT | 6 | BF-A | 5 | 2 | 112,5KVA | 1 | 7 | AV. | 71 | 7 | 1 | (DCIM) | C10x600,B1M,M3F | C12x300,CE-SH,ET4A,IP112,5KVAET4A112,5KVAIP | CONEX. | 112,5KVA | CONEX. | 7 | 1</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="n">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2 CS's (DCIM) (DCIM) 12 BT CONEX. 1RU6A 6112,5KVA0 (KL) 0 1112,5KVA(DCIM) (DCIM) 2 AVENIDA (DCIM) C12x300,CE-SH,ET4A,IP112,5KVAET4A112,5KVAIP | 27.63m P5 | CONEX. 1 7 2 CS's (DCIM) (DCIM) 12 1AF(1) CONEX. (KL) 600112,5KVACE4 | P6 1 2 QX16 RAMAL 2 V1-3 14M LC P5 | B1F (DCIM) BT BT 1 3 CONEX. CONEX. 3 7 CONEX. 0 1 112,5KVA 2 CONEX. 0 (DCIM) (DCIM) 5 7 112,5KVA 1x3x120(70)AX CRUZ 112,5KVA 1x4ANA | 1 | 112,5KVA 5 2 V1-3 6</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -741,20 +779,31 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>(DCIM) | (DCIM) | (DCIM) | (DCIM) | ANCORAR | CONEX. | ANCORAR | BF-A | BF-A | 4 | (DCIM) | 3 | 6 | (DCIM) | 3 | MT | 3 | (DCIM) | 0 | (DCIM) | 1 | 1 | ANCORAR | 3x185AX(5AZN) | 112,5KVA | 6 | ANCORAR | 6 | B1F | BF-A | 7 | CAMPO | 7 | BT | BF-A | NF | 1 | BF-A | 1x3x120(70)AX | 112,5KVA | 8 | 71 | 7 | 7 | 3 | 112,5KVA | 3 | 07 | 1 | 175ET005296879 | 2 | 1 | 1 | BF-A | 1 | 3 | 6 | 112,5KVA | 6 | 7 | 7 | CAMPO | 1 | 1 | 112,5KVA | 7 | BT | 17 | 1 | 5 | AVENIDA</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>C12X600112,5KVACE4112,5KVABF-A112,5KVAIP C09x300,SMPI,IP BT CARGA112,5KVA(KL) C09x300,SMPI,L1(2),IP | P1-11 | P2 | CONEX. MT 3x185AX(5AZN) | (DCIM) (DCIM) B1F BT 1x3x120(70)AX</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -782,20 +831,31 @@
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1 | RAMAL | TRAFO | 2 | TX16 | 2x1/0AN(4ANA) | 1 | TX10 | INSTALAÇÃO | BF-A | REAPROVEITAR | 36M | LC | BF-A | MV | 29M | 15KV_1T(ABC) | 175ET005296879 | 564661112,5KVAD_TF | (DCIM) | 12 | CONEX. | 6 | 0 | 0 | 112,5KVA</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2 CS's (DCIM) (DCIM) 12 BT CONEX. 1RU6A 6112,5KVA0 (KL) 0 1112,5KVA(DCIM) (DCIM) 2 AVENIDA (DCIM) C12x300,CE-SH,ET4A,IP112,5KVAET4A112,5KVAIP | C12X600112,5KVACE4112,5KVABF-A112,5KVAIP C09x300,SMPI,IP BT CARGA112,5KVA(KL) C09x300,SMPI,L1(2),IP | 1 RAMAL LC P5 | TRAFO 1x4ANA INSTALAÇÃO REAPROVEITAR | 175ET005296879 MV 564661112,5KVAD_TF 15KV_1T(ABC) | C10x600,B1M,M3F 2 V1-3 45KVA 13200 | 175ET005296879 5 6 4 6 6</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -821,30 +881,33 @@
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>(DCIM) | (DCIM) | (DCIM) | ANCORAR | (DCIM) | BF-A | ANCORAR | BF-A | 4 | 3 | 3 | 1 | 3 | 6 | 1 | 0 | 6 | 6 | CONEX. | 7 | BF-A | 112,5KVA | 7 | 1 | CAMPO | 7 | 71 | 112,5KVA | MT | (DCIM) | 1 | (DCIM) | NF | 1 | 3x185AX(5AZN) | 175ET005296879 | (DCIM) | (DCIM) | B1F | ANCORAR | BT | ANCORAR | 1x3x120(70)AX | BF-A | BF-A | C09x300,SMPI,IP | 8 | 5 | 112,5KVA | 7 | C12X600112,5KVACE4112,5KVABF-A112,5KVAIP | 2 | BF-A | 3 | 3 | 3 | BT | 07 | (DCIM) | 1 | BF-A | 1 | FERRAGEM112,5KVA(KL)</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="n">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>C12X600112,5KVACE4112,5KVABF-A112,5KVAIP C09x300,SMPI,IP BT CARGA112,5KVA(KL) C09x300,SMPI,L1(2),IP | P2 | P1-11 | 175ET005296879 112,5KVA CAMPO 112,5KVA 6 1 3 3 3 4 2 V1-3 | 1 71 7 1 7 6 1 | CONEX. MT 3x185AX(5AZN)</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
